--- a/RS_D620/documents/RS_620_scratchpad.xlsx
+++ b/RS_D620/documents/RS_620_scratchpad.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repo\POC\RS_D620\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27178B41-6DED-47DC-93E4-EABAFA4D5458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF7399D1-610A-42E9-9A06-E6397FB3040A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21285" yWindow="2940" windowWidth="21600" windowHeight="11295" xr2:uid="{77793D01-6217-42E2-9AFC-8B7FA38831D5}"/>
+    <workbookView xWindow="-21495" yWindow="2940" windowWidth="21600" windowHeight="11295" xr2:uid="{77793D01-6217-42E2-9AFC-8B7FA38831D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,6 +36,83 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+  <si>
+    <t>MON1</t>
+  </si>
+  <si>
+    <t>MON2</t>
+  </si>
+  <si>
+    <t>MON3</t>
+  </si>
+  <si>
+    <t>MON4</t>
+  </si>
+  <si>
+    <t>MON5</t>
+  </si>
+  <si>
+    <t>MON6</t>
+  </si>
+  <si>
+    <t>MON7</t>
+  </si>
+  <si>
+    <t>MON8</t>
+  </si>
+  <si>
+    <t>MON9</t>
+  </si>
+  <si>
+    <t>DMON1</t>
+  </si>
+  <si>
+    <t>…</t>
+  </si>
+  <si>
+    <t>DMON8</t>
+  </si>
+  <si>
+    <t>MON24</t>
+  </si>
+  <si>
+    <t>EN1</t>
+  </si>
+  <si>
+    <t>EN32</t>
+  </si>
+  <si>
+    <t>MAR1'</t>
+  </si>
+  <si>
+    <t>MAR16'</t>
+  </si>
+  <si>
+    <t>PMBUS_CLK</t>
+  </si>
+  <si>
+    <t>PMBUS_DATA</t>
+  </si>
+  <si>
+    <t>PMBUS_nALERT</t>
+  </si>
+  <si>
+    <t>PMBUS_ADDR0</t>
+  </si>
+  <si>
+    <t>PMBUS_ADDR1</t>
+  </si>
+  <si>
+    <t>PMBUS_ADDR2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -69,8 +146,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -405,9 +484,148 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2196B8D-FE2F-4541-9D73-52590DEE3D06}">
-  <dimension ref="A1"/>
+  <dimension ref="B3:B34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="16.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>